--- a/reports/TestReport.xlsx
+++ b/reports/TestReport.xlsx
@@ -463,22 +463,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -557,32 +557,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SMO-test_home</t>
+          <t>AUT-test_delete_account</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_home</t>
+          <t>test_delete_account</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Smoke</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>authentication</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -597,54 +597,1329 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>14:42:21</t>
+          <t>08:06:06</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_delete_account.py:21: in test_delete_account
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>tests/authentication/test_delete_account.py::test_delete_account</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>AUT-test_login</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>08:06:07</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_login.py:22: in test_login
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_login.py::test_login</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AUT-test_logout</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>test_logout</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>08:06:08</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_logout.py:21: in test_logout
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_logout.py::test_logout</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AUT-test_register</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>test_register</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>08:06:09</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_register.py:19: in test_register
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_register.py::test_register</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AUT-test_signup</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>test_signup</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>authentication</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>08:06:09</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_signup.py:8: in test_signup
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tests/authentication/test_signup.py::test_signup</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_continue_shopping</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>test_continue_shopping</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>08:06:10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_continue_shopping.py:17: in test_continue_shopping
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_continue_shopping.py::test_continue_shopping</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_multiple_products</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>test_multiple_products</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>08:06:11</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_multiple_products.py:17: in test_multiple_products
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_multiple_products.py::test_multiple_products</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_proceed_to_checkout</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>test_proceed_to_checkout</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>08:06:12</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_proceed_to_checkout.py:28: in test_proceed_to_checkout
+    signup.open()
+pages/authentication/signup_page.py:36: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_proceed_to_checkout.py::test_proceed_to_checkout</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_remove_product</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>test_remove_product</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>08:06:13</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_remove_product.py:17: in test_remove_product
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_remove_product.py::test_remove_product</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_verify_cart_information</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>test_verify_cart_information</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>08:06:14</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_verify_cart_information.py:17: in test_verify_cart_information
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_verify_cart_information.py::test_verify_cart_information</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CAR-test_view_cart</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>test_view_cart</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Cart</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cart</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>08:06:14</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_view_cart.py:17: in test_view_cart
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tests/cart/test_view_cart.py::test_view_cart</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PRO-test_add_to_cart</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>test_add_to_cart</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>08:06:15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_add_to_cart.py:11: in test_add_to_cart
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_add_to_cart.py::test_add_to_cart</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PRO-test_search_product</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>test_search_product</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>08:06:16</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_search_product.py:16: in test_search_product
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_search_product.py::test_search_product</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PRO-test_view_products</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>test_view_products</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>08:06:17</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_view_product.py:11: in test_view_products
+    product.open()
+pages/product/product_page.py:66: in open
+    self.visit(self.URL)
+utils/base_page.py:24: in visit
+    self.page.goto(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/products
+E   Call log:
+E     - navigating to "https://automationexercise.com/products", waiting until "domcontentloaded"</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tests/product/test_view_product.py::test_view_products</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SMO-test_home</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>test_home</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>08:06:18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tests/smoke/test_home.py:6: in test_home
+    page.goto(BASE_URL)
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:9770: in goto
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_page.py:560: in goto
+    return await self._main_frame.goto(**locals_to_params(locals()))
+           ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_frame.py:156: in goto
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.Error: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://automationexercise.com/
+E   Call log:
+E     - navigating to "https://automationexercise.com/", waiting until "load"</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>tests/smoke/test_home.py::test_home</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>local</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TES-test_open</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>test_open</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Test_open.py</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>test_open.py</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>msedge</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>08:06:18</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_open.py:9: in test_open
+    browser = p.chromium.launch(
+../../../.local/lib/python3.12/site-packages/playwright/sync_api/_generated.py:16515: in launch
+    self._sync(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_browser_type.py:97: in launch
+    await self._channel.send(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:69: in send
+    return await self._connection.wrap_api_call(
+../../../.local/lib/python3.12/site-packages/playwright/_impl/_connection.py:563: in wrap_api_call
+    raise rewrite_error(error, f"{parsed_st['apiName']}: {error}") from None
+E   playwright._impl._errors.TargetClosedError: BrowserType.launch: Target page, context or browser has been closed
+E   Browser logs:
+E   
+E   ╔════════════════════════════════════════════════════════════════════════════════════════════════╗
+E   ║ Looks like you launched a headed browser without having a XServer running.                     ║
+E   ║ Set either 'headless: true' or use 'xvfb-run &lt;your-playwright-app&gt;' before running Playwright. ║
+E   ║                                                                                                ║
+E   ║ &lt;3 Playwright Team                                                                             ║
+E   ╚════════════════════════════════════════════════════════════════════════════════════════════════╝
+E   Call log:
+E     - &lt;launching&gt; /home/runner/.cache/ms-playwright/chromium-1228/chrome-linux64/chrome --disable-field-trial-config --disable-background-networking --disable-background-timer-throttling --disable-backgrounding-occluded-windows --disable-back-forward-cache --disable-breakpad --disable-client-side-phishing-detection --disable-component-extensions-with-background-pages --disable-component-update --no-default-browser-check --disable-default-apps --disable-dev-shm-usage --disable-edgeupdater --disable-extensions --disable-features=AvoidUnnecessaryBeforeUnloadCheckSync,BoundaryEventDispatchTracksNodeRemoval,DestroyProfileOnBrowserClose,DialMediaRouteProvider,GlobalMediaControls,HttpsUpgrades,LensOverlay,MediaRouter,PaintHolding,ThirdPartyStoragePartitioning,Translate,AutoDeElevate,RenderDocument,OptimizationHints,msForceBrowserSignIn,msEdgeUpdateLaunchServicesPreferredVersion --enable-features=CDPScreenshotNewSurface --allow-pre-commit-input --disable-hang-monitor --disable-ipc-flooding-protection --disable-popup-blocking --disable-prompt-on-repost --disable-renderer-backgrounding --force-color-profile=srgb --metrics-recording-only --no-first-run --password-store=basic --use-mock-keychain --no-service-autorun --export-tagged-pdf --disable-search-engine-choice-screen --unsafely-disable-devtools-self-xss-warnings --edge-skip-compat-layer-relaunch --disable-infobars --disable-search-engine-choice-screen --disable-sync --enable-unsafe-swiftshader --no-sandbox --user-data-dir=/tmp/playwright_chromiumdev_profile-jujYgp --remote-debugging-pipe --no-startup-window
+E     - &lt;launched&gt; pid=5269
+E     - [pid=5269][err] [5269:5269:0704/080618.712499:ERROR:ui/ozone/platform/x11/ozone_platform_x11.cc:257] Missing X server or $DISPLAY
+E     - [pid=5269][err] [5269:5269:0704/080618.712532:ERROR:ui/aura/env.cc:246] The platform failed to initialize.  Exiting.
+E     - [pid=5269] &lt;gracefully close start&gt;
+E     - [pid=5269] &lt;kill&gt;
+E     - [pid=5269] &lt;will force kill&gt;
+E     - [pid=5269] &lt;process did exit: exitCode=1, signal=null&gt;
+E     - [pid=5269] starting temporary directories cleanup
+E     - [pid=5269] finished temporary directories cleanup
+E     - [pid=5269] &lt;gracefully close end&gt;</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_open.py::test_open</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL: 1</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PASSED: 1</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FAILED: 0</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL: 16</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PASSED: 0</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>FAILED: 16</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>SKIPPED: 0</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
